--- a/AAAGameData/DataTables/ArrowGuideTable.xlsx
+++ b/AAAGameData/DataTables/ArrowGuideTable.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\DataTables\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="23040" windowHeight="16635"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -137,25 +142,10 @@
     <t>0,-429</t>
   </si>
   <si>
+    <t>GuidTxt2</t>
+  </si>
+  <si>
     <t>0,400</t>
-  </si>
-  <si>
-    <t>GuidTxt3</t>
-  </si>
-  <si>
-    <t>0,0</t>
-  </si>
-  <si>
-    <t>GuidTxt4</t>
-  </si>
-  <si>
-    <t>0,150</t>
-  </si>
-  <si>
-    <t>GuidTxt5</t>
-  </si>
-  <si>
-    <t>GuidTxt6</t>
   </si>
 </sst>
 </file>
@@ -1323,8 +1313,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="33.4285714285714" style="1" customWidth="1"/>
@@ -1433,7 +1423,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1" t="b">
         <v>0</v>
@@ -1456,16 +1446,19 @@
         <v>2</v>
       </c>
       <c r="E6" s="1">
+        <v>2</v>
+      </c>
+      <c r="F6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="b">
         <v>1</v>
-      </c>
-      <c r="F6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="b">
-        <v>0</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1473,111 +1466,19 @@
         <v>3</v>
       </c>
       <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1">
         <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
       </c>
       <c r="F7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:11">
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="D8" s="1">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="B9" s="1">
-        <v>5</v>
-      </c>
-      <c r="D9" s="1">
-        <v>2</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="B10" s="1">
-        <v>6</v>
-      </c>
-      <c r="D10" s="1">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1">
-        <v>2</v>
-      </c>
-      <c r="F10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="B11" s="1">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/ArrowGuideTable.xlsx
+++ b/AAAGameData/DataTables/ArrowGuideTable.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="16635"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -1313,8 +1313,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="6"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
     <col min="4" max="4" width="33.4285714285714" style="1" customWidth="1"/>
@@ -1481,6 +1481,23 @@
         <v>24</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="1">
+        <v>4</v>
+      </c>
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1">
+        <v>1</v>
+      </c>
+      <c r="F8" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" sqref="D1:AB1">

--- a/AAAGameData/DataTables/ArrowGuideTable.xlsx
+++ b/AAAGameData/DataTables/ArrowGuideTable.xlsx
@@ -133,13 +133,13 @@
     <t>文本内容（多语言Key）</t>
   </si>
   <si>
-    <t>0,-590</t>
+    <t>0,300</t>
   </si>
   <si>
     <t>GuidTxt1</t>
   </si>
   <si>
-    <t>0,-429</t>
+    <t>0,-200</t>
   </si>
   <si>
     <t>GuidTxt2</t>
